--- a/Kachi_Gun/Table/Weapon_Enchant.xlsx
+++ b/Kachi_Gun/Table/Weapon_Enchant.xlsx
@@ -605,14 +605,14 @@
         <v>20</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1000</v>
+        <v>46200</v>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>46.2k</t>
         </is>
       </c>
       <c r="I2" s="7" t="n">
@@ -654,14 +654,14 @@
         <v>40</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.18</v>
+        <v>11.9264</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1180</v>
+        <v>551000</v>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>1.18k</t>
+          <t>551k</t>
         </is>
       </c>
       <c r="I3" s="7" t="n">
@@ -703,14 +703,14 @@
         <v>60</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.18</v>
+        <v>3.0853</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1392</v>
+        <v>1700000</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>1.39k</t>
+          <t>1.7m</t>
         </is>
       </c>
       <c r="I4" s="7" t="n">
@@ -752,14 +752,14 @@
         <v>85</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.18</v>
+        <v>2.1471</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1643</v>
+        <v>3650000</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>1.64k</t>
+          <t>3.65m</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
@@ -801,14 +801,14 @@
         <v>110</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.18</v>
+        <v>5.2055</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1939</v>
+        <v>19000000</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>1.93k</t>
+          <t>19m</t>
         </is>
       </c>
       <c r="I6" s="7" t="n">
@@ -850,14 +850,14 @@
         <v>135</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.18</v>
+        <v>4.0158</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2288</v>
+        <v>76300000</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>2.28k</t>
+          <t>76.3m</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -899,14 +899,14 @@
         <v>160</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.18</v>
+        <v>3.8663</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2700</v>
+        <v>295000000</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>2.69k</t>
+          <t>295m</t>
         </is>
       </c>
       <c r="I8" s="7" t="n">
@@ -948,14 +948,14 @@
         <v>190</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.18</v>
+        <v>6.4068</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>3185</v>
+        <v>1890000000</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>3.18k</t>
+          <t>1.89b</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">
@@ -997,14 +997,14 @@
         <v>220</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.18</v>
+        <v>2.0159</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>3759</v>
+        <v>3810000000</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>3.75k</t>
+          <t>3.81b</t>
         </is>
       </c>
       <c r="I10" s="7" t="n">
@@ -1046,14 +1046,14 @@
         <v>250</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.18</v>
+        <v>3.3071</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>4435</v>
+        <v>12600000000</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>4.43k</t>
+          <t>12.6b</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
@@ -1095,14 +1095,14 @@
         <v>285</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.18</v>
+        <v>1.6349</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>5234</v>
+        <v>20600000000</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>5.23k</t>
+          <t>20.6b</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
@@ -1144,14 +1144,14 @@
         <v>320</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.18</v>
+        <v>3.4515</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>6176</v>
+        <v>71100000000</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>6.17k</t>
+          <t>71.1b</t>
         </is>
       </c>
       <c r="I13" s="7" t="n">
@@ -1193,14 +1193,14 @@
         <v>355</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.18</v>
+        <v>1.3066</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>7288</v>
+        <v>92900000000</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>7.28k</t>
+          <t>92.9b</t>
         </is>
       </c>
       <c r="I14" s="7" t="n">
@@ -1242,14 +1242,14 @@
         <v>395</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.18</v>
+        <v>3.6491</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>8599</v>
+        <v>339000000000</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>8.59k</t>
+          <t>339b</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
@@ -1291,14 +1291,14 @@
         <v>435</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.18</v>
+        <v>1.4867</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>10147</v>
+        <v>504000000000</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>10.1k</t>
+          <t>504b</t>
         </is>
       </c>
       <c r="I16" s="7" t="n">
@@ -1340,14 +1340,14 @@
         <v>475</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.18</v>
+        <v>3.7103</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>11974</v>
+        <v>1870000000000</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>11.9k</t>
+          <t>1.87t</t>
         </is>
       </c>
       <c r="I17" s="7" t="n">
@@ -1389,14 +1389,14 @@
         <v>520</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.18</v>
+        <v>1.5561</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>14129</v>
+        <v>2910000000000</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>14.1k</t>
+          <t>2.91t</t>
         </is>
       </c>
       <c r="I18" s="7" t="n">
@@ -1438,14 +1438,14 @@
         <v>565</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.18</v>
+        <v>4.5361</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>16672</v>
+        <v>13200000000000</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>16.6k</t>
+          <t>13.2t</t>
         </is>
       </c>
       <c r="I19" s="7" t="n">
@@ -1487,14 +1487,14 @@
         <v>615</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.18</v>
+        <v>1.1515</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>19673</v>
+        <v>15200000000000</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>19.6k</t>
+          <t>15.2t</t>
         </is>
       </c>
       <c r="I20" s="7" t="n">
@@ -1536,14 +1536,14 @@
         <v>665</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.18</v>
+        <v>3.8684</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>23214</v>
+        <v>58800000000000</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>23.2k</t>
+          <t>58.8t</t>
         </is>
       </c>
       <c r="I21" s="7" t="n">
@@ -1585,14 +1585,14 @@
         <v>720</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.18</v>
+        <v>1.0068</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>27393</v>
+        <v>59200000000000</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>27.3k</t>
+          <t>59.2t</t>
         </is>
       </c>
       <c r="I22" s="7" t="n">
@@ -1634,14 +1634,14 @@
         <v>775</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.18</v>
+        <v>2.1791</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>32324</v>
+        <v>129000000000000</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>32.3k</t>
+          <t>129t</t>
         </is>
       </c>
       <c r="I23" s="7" t="n">
@@ -1683,14 +1683,14 @@
         <v>835</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.18</v>
+        <v>2.3721</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>38142</v>
+        <v>306000000000000</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>38.1k</t>
+          <t>306t</t>
         </is>
       </c>
       <c r="I24" s="7" t="n">
@@ -1732,14 +1732,14 @@
         <v>895</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.18</v>
+        <v>2.1569</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>45008</v>
+        <v>660000000000000</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>45k</t>
+          <t>660t</t>
         </is>
       </c>
       <c r="I25" s="7" t="n">
@@ -1781,14 +1781,14 @@
         <v>960</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.18</v>
+        <v>2.3788</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>53109</v>
+        <v>1570000000000000</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>53.1k</t>
+          <t>1.57aa</t>
         </is>
       </c>
       <c r="I26" s="7" t="n">
@@ -1830,14 +1830,14 @@
         <v>1030</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.18</v>
+        <v>3.3248</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>62669</v>
+        <v>5220000000000000</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>62.6k</t>
+          <t>5.22aa</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
@@ -1879,14 +1879,14 @@
         <v>1100</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2395</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>73949</v>
+        <v>6470000000000000</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>73.9k</t>
+          <t>6.47aa</t>
         </is>
       </c>
       <c r="I28" s="7" t="n">
@@ -1928,14 +1928,14 @@
         <v>1175</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.18</v>
+        <v>1.7156</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>87260</v>
+        <v>1.11e+16</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>87.2k</t>
+          <t>11.1aa</t>
         </is>
       </c>
       <c r="I29" s="7" t="n">
@@ -1977,14 +1977,14 @@
         <v>1255</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.18</v>
+        <v>1.8919</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>102967</v>
+        <v>2.1e+16</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>102k</t>
+          <t>21aa</t>
         </is>
       </c>
       <c r="I30" s="7" t="n">
@@ -2026,14 +2026,14 @@
         <v>1335</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.18</v>
+        <v>1.7952</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>121501</v>
+        <v>3.77e+16</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>121k</t>
+          <t>37.7aa</t>
         </is>
       </c>
       <c r="I31" s="7" t="n">
@@ -2075,14 +2075,14 @@
         <v>1420</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.18</v>
+        <v>1.5756</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>143371</v>
+        <v>5.94e+16</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>143k</t>
+          <t>59.4aa</t>
         </is>
       </c>
       <c r="I32" s="7" t="n">
@@ -2124,14 +2124,14 @@
         <v>1510</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.18</v>
+        <v>1.8687</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>169177</v>
+        <v>1.11e+17</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>169k</t>
+          <t>111aa</t>
         </is>
       </c>
       <c r="I33" s="7" t="n">
@@ -2173,14 +2173,14 @@
         <v>1605</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.18</v>
+        <v>1.8108</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>199629</v>
+        <v>2.01e+17</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>199k</t>
+          <t>201aa</t>
         </is>
       </c>
       <c r="I34" s="7" t="n">
@@ -2222,14 +2222,14 @@
         <v>1705</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.18</v>
+        <v>1.806</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>235563</v>
+        <v>3.63e+17</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>235k</t>
+          <t>363aa</t>
         </is>
       </c>
       <c r="I35" s="7" t="n">
@@ -2271,14 +2271,14 @@
         <v>1810</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1.18</v>
+        <v>1.6749</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>277964</v>
+        <v>6.08e+17</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>277k</t>
+          <t>608aa</t>
         </is>
       </c>
       <c r="I36" s="7" t="n">
@@ -2320,14 +2320,14 @@
         <v>1920</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.18</v>
+        <v>1.7434</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>327997</v>
+        <v>1.06e+18</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>327k</t>
+          <t>1.06ab</t>
         </is>
       </c>
       <c r="I37" s="7" t="n">
@@ -2369,14 +2369,14 @@
         <v>2035</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1.18</v>
+        <v>2.3019</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>387037</v>
+        <v>2.44e+18</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>387k</t>
+          <t>2.44ab</t>
         </is>
       </c>
       <c r="I38" s="7" t="n">
@@ -2418,14 +2418,14 @@
         <v>2155</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.18</v>
+        <v>1.582</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>456703</v>
+        <v>3.86e+18</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>456k</t>
+          <t>3.86ab</t>
         </is>
       </c>
       <c r="I39" s="7" t="n">
@@ -2467,14 +2467,14 @@
         <v>2285</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1.18</v>
+        <v>1.8238</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>538910</v>
+        <v>7.04e+18</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>538k</t>
+          <t>7.04ab</t>
         </is>
       </c>
       <c r="I40" s="7" t="n">
@@ -2516,14 +2516,14 @@
         <v>2420</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1.18</v>
+        <v>1.9176</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>635914</v>
+        <v>1.35e+19</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>635k</t>
+          <t>13.5ab</t>
         </is>
       </c>
       <c r="I41" s="7" t="n">
@@ -2565,14 +2565,14 @@
         <v>2560</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.18</v>
+        <v>1.5185</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>750378</v>
+        <v>2.05e+19</v>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>750k</t>
+          <t>20.5ab</t>
         </is>
       </c>
       <c r="I42" s="7" t="n">
@@ -2614,14 +2614,14 @@
         <v>2710</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1.18</v>
+        <v>1.8049</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>885446</v>
+        <v>3.7e+19</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>885k</t>
+          <t>37ab</t>
         </is>
       </c>
       <c r="I43" s="7" t="n">
@@ -2663,14 +2663,14 @@
         <v>2865</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1.18</v>
+        <v>1.9486</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1044827</v>
+        <v>7.21e+19</v>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>1.04m</t>
+          <t>72.1ab</t>
         </is>
       </c>
       <c r="I44" s="7" t="n">
@@ -2712,14 +2712,14 @@
         <v>3030</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1.18</v>
+        <v>1.595</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1232896</v>
+        <v>1.15e+20</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>1.23m</t>
+          <t>115ab</t>
         </is>
       </c>
       <c r="I45" s="7" t="n">
@@ -2761,14 +2761,14 @@
         <v>3200</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1.18</v>
+        <v>2.0957</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1454817</v>
+        <v>2.41e+20</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>1.45m</t>
+          <t>241ab</t>
         </is>
       </c>
       <c r="I46" s="7" t="n">
@@ -2810,14 +2810,14 @@
         <v>3380</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.18</v>
+        <v>1.6515</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1716684</v>
+        <v>3.98e+20</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>1.71m</t>
+          <t>398ab</t>
         </is>
       </c>
       <c r="I47" s="7" t="n">
@@ -2859,14 +2859,14 @@
         <v>3570</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1.18</v>
+        <v>2.005</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2025687</v>
+        <v>7.98e+20</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>2.02m</t>
+          <t>798ab</t>
         </is>
       </c>
       <c r="I48" s="7" t="n">
@@ -2908,14 +2908,14 @@
         <v>3770</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.18</v>
+        <v>1.3283</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2390311</v>
+        <v>1.06e+21</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>2.39m</t>
+          <t>1.06ac</t>
         </is>
       </c>
       <c r="I49" s="7" t="n">
@@ -2957,14 +2957,14 @@
         <v>3980</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1.18</v>
+        <v>3.0755</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2820567</v>
+        <v>3.26e+21</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>2.82m</t>
+          <t>3.26ac</t>
         </is>
       </c>
       <c r="I50" s="7" t="n">
@@ -3006,14 +3006,14 @@
         <v>4200</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.18</v>
+        <v>1.0368</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>3328269</v>
+        <v>3.38e+21</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>3.32m</t>
+          <t>3.38ac</t>
         </is>
       </c>
       <c r="I51" s="7" t="n">
@@ -3055,14 +3055,14 @@
         <v>4425</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1.12</v>
+        <v>2.3402</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>3727661</v>
+        <v>7.910000000000001e+21</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>3.72m</t>
+          <t>7.91ac</t>
         </is>
       </c>
       <c r="I52" s="7" t="n">
@@ -3104,14 +3104,14 @@
         <v>4660</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0202</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>4174980</v>
+        <v>8.070000000000001e+21</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>4.17m</t>
+          <t>8.07ac</t>
         </is>
       </c>
       <c r="I53" s="7" t="n">
@@ -3153,14 +3153,14 @@
         <v>4900</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0248</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>4675978</v>
+        <v>8.270000000000001e+21</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>4.67m</t>
+          <t>8.27ac</t>
         </is>
       </c>
       <c r="I54" s="7" t="n">
@@ -3202,14 +3202,14 @@
         <v>5150</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.12</v>
+        <v>1.9347</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>5237095</v>
+        <v>1.6e+22</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>5.23m</t>
+          <t>16ac</t>
         </is>
       </c>
       <c r="I55" s="7" t="n">
@@ -3251,14 +3251,14 @@
         <v>5410</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1.12</v>
+        <v>1.1188</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>5865546</v>
+        <v>1.79e+22</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>5.86m</t>
+          <t>17.9ac</t>
         </is>
       </c>
       <c r="I56" s="7" t="n">
@@ -3300,14 +3300,14 @@
         <v>5680</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1.12</v>
+        <v>1.2682</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>6569412</v>
+        <v>2.27e+22</v>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>6.56m</t>
+          <t>22.7ac</t>
         </is>
       </c>
       <c r="I57" s="7" t="n">
@@ -3349,14 +3349,14 @@
         <v>5960</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1.12</v>
+        <v>1.4185</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>7357741</v>
+        <v>3.22e+22</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>7.35m</t>
+          <t>32.1ac</t>
         </is>
       </c>
       <c r="I58" s="7" t="n">
@@ -3398,14 +3398,14 @@
         <v>6250</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1.12</v>
+        <v>2.5124</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>8240670</v>
+        <v>8.090000000000001e+22</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>8.24m</t>
+          <t>80.9ac</t>
         </is>
       </c>
       <c r="I59" s="7" t="n">
@@ -3447,14 +3447,14 @@
         <v>6550</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0161</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>9229551</v>
+        <v>8.219999999999999e+22</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>9.22m</t>
+          <t>82.1ac</t>
         </is>
       </c>
       <c r="I60" s="7" t="n">
@@ -3496,14 +3496,14 @@
         <v>6860</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1.12</v>
+        <v>1.399</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>10337097</v>
+        <v>1.15e+23</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>10.3m</t>
+          <t>115ac</t>
         </is>
       </c>
       <c r="I61" s="7" t="n">
@@ -3545,14 +3545,14 @@
         <v>7180</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0261</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>11577548</v>
+        <v>1.18e+23</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>11.5m</t>
+          <t>118ac</t>
         </is>
       </c>
       <c r="I62" s="7" t="n">
@@ -3594,14 +3594,14 @@
         <v>7510</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1.12</v>
+        <v>2.4915</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>12966854</v>
+        <v>2.94e+23</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>12.9m</t>
+          <t>294ac</t>
         </is>
       </c>
       <c r="I63" s="7" t="n">
@@ -3643,14 +3643,14 @@
         <v>7850</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0306</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>14522877</v>
+        <v>3.03e+23</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>14.5m</t>
+          <t>303ac</t>
         </is>
       </c>
       <c r="I64" s="7" t="n">
@@ -3692,14 +3692,14 @@
         <v>8205</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0363</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>16265622</v>
+        <v>3.14e+23</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>16.2m</t>
+          <t>314ac</t>
         </is>
       </c>
       <c r="I65" s="7" t="n">
@@ -3741,14 +3741,14 @@
         <v>8570</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1.12</v>
+        <v>1.3057</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>18217497</v>
+        <v>4.1e+23</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>18.2m</t>
+          <t>410ac</t>
         </is>
       </c>
       <c r="I66" s="7" t="n">
@@ -3790,14 +3790,14 @@
         <v>8950</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.12</v>
+        <v>1.5561</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>20403596</v>
+        <v>6.38e+23</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>20.4m</t>
+          <t>638ac</t>
         </is>
       </c>
       <c r="I67" s="7" t="n">
@@ -3839,14 +3839,14 @@
         <v>9340</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1.12</v>
+        <v>1.2539</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>22852028</v>
+        <v>7.999999999999999e+23</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>22.8m</t>
+          <t>799ac</t>
         </is>
       </c>
       <c r="I68" s="7" t="n">
@@ -3888,14 +3888,14 @@
         <v>9745</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>25594271</v>
+        <v>1.16e+24</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>25.5m</t>
+          <t>1.16ad</t>
         </is>
       </c>
       <c r="I69" s="7" t="n">
@@ -3937,14 +3937,14 @@
         <v>10165</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1.12</v>
+        <v>2.7672</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>28665584</v>
+        <v>3.21e+24</v>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>28.6m</t>
+          <t>3.21ad</t>
         </is>
       </c>
       <c r="I70" s="7" t="n">
@@ -3986,14 +3986,14 @@
         <v>10600</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0218</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>32105454</v>
+        <v>3.28e+24</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>32.1m</t>
+          <t>3.28ad</t>
         </is>
       </c>
       <c r="I71" s="7" t="n">
@@ -4035,14 +4035,14 @@
         <v>11050</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0274</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>35958108</v>
+        <v>3.37e+24</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>35.9m</t>
+          <t>3.37ad</t>
         </is>
       </c>
       <c r="I72" s="7" t="n">
@@ -4084,14 +4084,14 @@
         <v>11515</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1.12</v>
+        <v>1.4154</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>40273081</v>
+        <v>4.77e+24</v>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>40.2m</t>
+          <t>4.77ad</t>
         </is>
       </c>
       <c r="I73" s="7" t="n">
@@ -4133,14 +4133,14 @@
         <v>11995</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1.12</v>
+        <v>1.2516</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>45105851</v>
+        <v>5.97e+24</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>45.1m</t>
+          <t>5.97ad</t>
         </is>
       </c>
       <c r="I74" s="7" t="n">
@@ -4182,14 +4182,14 @@
         <v>12495</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1.12</v>
+        <v>1.8928</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>50518553</v>
+        <v>1.13e+25</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>50.5m</t>
+          <t>11.3ad</t>
         </is>
       </c>
       <c r="I75" s="7" t="n">
@@ -4231,14 +4231,14 @@
         <v>13010</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0442</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>56580779</v>
+        <v>1.18e+25</v>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>56.5m</t>
+          <t>11.7ad</t>
         </is>
       </c>
       <c r="I76" s="7" t="n">
@@ -4280,14 +4280,14 @@
         <v>13545</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.12</v>
+        <v>1.3644</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>63370473</v>
+        <v>1.61e+25</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>63.3m</t>
+          <t>16.1ad</t>
         </is>
       </c>
       <c r="I77" s="7" t="n">
@@ -4329,14 +4329,14 @@
         <v>14100</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1.12</v>
+        <v>1.323</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>70974930</v>
+        <v>2.13e+25</v>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>70.9m</t>
+          <t>21.3ad</t>
         </is>
       </c>
       <c r="I78" s="7" t="n">
@@ -4378,14 +4378,14 @@
         <v>14670</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1.12</v>
+        <v>1.6244</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>79491921</v>
+        <v>3.46e+25</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>79.4m</t>
+          <t>34.6ad</t>
         </is>
       </c>
       <c r="I79" s="7" t="n">
@@ -4427,14 +4427,14 @@
         <v>15260</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1.12</v>
+        <v>1.2486</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>89030952</v>
+        <v>4.32e+25</v>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>89m</t>
+          <t>43.2ad</t>
         </is>
       </c>
       <c r="I80" s="7" t="n">
@@ -4476,14 +4476,14 @@
         <v>15875</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1.12</v>
+        <v>1.4375</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>99714666</v>
+        <v>6.21e+25</v>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>99.7m</t>
+          <t>62.1ad</t>
         </is>
       </c>
       <c r="I81" s="7" t="n">
@@ -4525,14 +4525,14 @@
         <v>16510</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.12</v>
+        <v>1.4976</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>111680426</v>
+        <v>9.3e+25</v>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>111m</t>
+          <t>93ad</t>
         </is>
       </c>
       <c r="I82" s="7" t="n">
@@ -4574,14 +4574,14 @@
         <v>17165</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1.12</v>
+        <v>2.0538</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>125082077</v>
+        <v>1.91e+26</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>125m</t>
+          <t>191ad</t>
         </is>
       </c>
       <c r="I83" s="7" t="n">
@@ -4623,14 +4623,14 @@
         <v>17845</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0105</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>140091926</v>
+        <v>1.93e+26</v>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>140m</t>
+          <t>193ad</t>
         </is>
       </c>
       <c r="I84" s="7" t="n">
@@ -4672,14 +4672,14 @@
         <v>18550</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1.12</v>
+        <v>1.3938</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>156902957</v>
+        <v>2.69e+26</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>156m</t>
+          <t>269ad</t>
         </is>
       </c>
       <c r="I85" s="7" t="n">
@@ -4721,14 +4721,14 @@
         <v>19280</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1.12</v>
+        <v>1.6952</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>175731312</v>
+        <v>4.56e+26</v>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>175m</t>
+          <t>456ad</t>
         </is>
       </c>
       <c r="I86" s="7" t="n">
@@ -4770,14 +4770,14 @@
         <v>20035</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0285</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>196819069</v>
+        <v>4.69e+26</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>196m</t>
+          <t>469ad</t>
         </is>
       </c>
       <c r="I87" s="7" t="n">
@@ -4819,14 +4819,14 @@
         <v>20815</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1.12</v>
+        <v>1.3412</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>220437358</v>
+        <v>6.29e+26</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>220m</t>
+          <t>629ad</t>
         </is>
       </c>
       <c r="I88" s="7" t="n">
@@ -4868,14 +4868,14 @@
         <v>21620</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1.12</v>
+        <v>1.496</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>246889841</v>
+        <v>9.41e+26</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>246m</t>
+          <t>941ad</t>
         </is>
       </c>
       <c r="I89" s="7" t="n">
@@ -4917,14 +4917,14 @@
         <v>22455</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1.12</v>
+        <v>1.3496</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>276516622</v>
+        <v>1.27e+27</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>276m</t>
+          <t>1.26ae</t>
         </is>
       </c>
       <c r="I90" s="7" t="n">
@@ -4966,14 +4966,14 @@
         <v>23320</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1.12</v>
+        <v>1.4961</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>309698616</v>
+        <v>1.9e+27</v>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>309m</t>
+          <t>1.9ae</t>
         </is>
       </c>
       <c r="I91" s="7" t="n">
@@ -5015,14 +5015,14 @@
         <v>24215</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1.12</v>
+        <v>1.4211</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>346862450</v>
+        <v>2.7e+27</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>346m</t>
+          <t>2.7ae</t>
         </is>
       </c>
       <c r="I92" s="7" t="n">
@@ -5064,14 +5064,14 @@
         <v>25140</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1.12</v>
+        <v>1.4593</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>388485944</v>
+        <v>3.94e+27</v>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>388m</t>
+          <t>3.94ae</t>
         </is>
       </c>
       <c r="I93" s="7" t="n">
@@ -5113,14 +5113,14 @@
         <v>26100</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1.12</v>
+        <v>2.0838</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>435104257</v>
+        <v>8.21e+27</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>435m</t>
+          <t>8.21ae</t>
         </is>
       </c>
       <c r="I94" s="7" t="n">
@@ -5162,14 +5162,14 @@
         <v>27090</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0037</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>487316768</v>
+        <v>8.24e+27</v>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>487m</t>
+          <t>8.24ae</t>
         </is>
       </c>
       <c r="I95" s="7" t="n">
@@ -5211,14 +5211,14 @@
         <v>28115</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>545794781</v>
+        <v>1.03e+28</v>
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>545m</t>
+          <t>10.2ae</t>
         </is>
       </c>
       <c r="I96" s="7" t="n">
@@ -5260,14 +5260,14 @@
         <v>29180</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1.12</v>
+        <v>2.165</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>611290154</v>
+        <v>2.23e+28</v>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>611m</t>
+          <t>22.3ae</t>
         </is>
       </c>
       <c r="I97" s="7" t="n">
@@ -5309,14 +5309,14 @@
         <v>30280</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1.12</v>
+        <v>1.0135</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>684644973</v>
+        <v>2.26e+28</v>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>684m</t>
+          <t>22.6ae</t>
         </is>
       </c>
       <c r="I98" s="7" t="n">
@@ -5358,14 +5358,14 @@
         <v>31420</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1.12</v>
+        <v>1.2124</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>766802369</v>
+        <v>2.74e+28</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>766m</t>
+          <t>27.4ae</t>
         </is>
       </c>
       <c r="I99" s="7" t="n">
@@ -5407,14 +5407,14 @@
         <v>32600</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1.12</v>
+        <v>1.3942</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>858818654</v>
+        <v>3.82e+28</v>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>858m</t>
+          <t>38.2ae</t>
         </is>
       </c>
       <c r="I100" s="7" t="n">
@@ -5456,14 +5456,14 @@
         <v>33820</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1.12</v>
+        <v>1.4188</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>961876892</v>
+        <v>5.42e+28</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>961m</t>
+          <t>54.2ae</t>
         </is>
       </c>
       <c r="I101" s="7" t="n">
@@ -5505,14 +5505,14 @@
         <v>35070</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1.08</v>
+        <v>1.4668</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1038827044</v>
+        <v>7.95e+28</v>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>1.03b</t>
+          <t>79.5ae</t>
         </is>
       </c>
       <c r="I102" s="7" t="n">
@@ -5554,14 +5554,14 @@
         <v>36350</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1.08</v>
+        <v>1.4214</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1121933207</v>
+        <v>1.13e+29</v>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>1.12b</t>
+          <t>113ae</t>
         </is>
       </c>
       <c r="I103" s="7" t="n">
@@ -5603,14 +5603,14 @@
         <v>37665</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1.08</v>
+        <v>1.2832</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1211687864</v>
+        <v>1.45e+29</v>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>1.21b</t>
+          <t>145ae</t>
         </is>
       </c>
       <c r="I104" s="7" t="n">
@@ -5652,14 +5652,14 @@
         <v>39010</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3793</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1308622893</v>
+        <v>2e+29</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>1.3b</t>
+          <t>199ae</t>
         </is>
       </c>
       <c r="I105" s="7" t="n">
@@ -5701,14 +5701,14 @@
         <v>40390</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1.08</v>
+        <v>2.73</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1413312724</v>
+        <v>5.46e+29</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>1.41b</t>
+          <t>546ae</t>
         </is>
       </c>
       <c r="I106" s="7" t="n">
@@ -5750,14 +5750,14 @@
         <v>41805</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1.08</v>
+        <v>1.011</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1526377742</v>
+        <v>5.52e+29</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>1.52b</t>
+          <t>552ae</t>
         </is>
       </c>
       <c r="I107" s="7" t="n">
@@ -5799,14 +5799,14 @@
         <v>43255</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0109</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1648487961</v>
+        <v>5.58e+29</v>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>1.64b</t>
+          <t>558ae</t>
         </is>
       </c>
       <c r="I108" s="7" t="n">
@@ -5848,14 +5848,14 @@
         <v>44740</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3853</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1780366998</v>
+        <v>7.729999999999999e+29</v>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>1.78b</t>
+          <t>772ae</t>
         </is>
       </c>
       <c r="I109" s="7" t="n">
@@ -5897,14 +5897,14 @@
         <v>46265</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0207</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>1922796358</v>
+        <v>7.889999999999999e+29</v>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>1.92b</t>
+          <t>788ae</t>
         </is>
       </c>
       <c r="I110" s="7" t="n">
@@ -5946,14 +5946,14 @@
         <v>47825</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>2076620067</v>
+        <v>8.600000000000001e+29</v>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>2.07b</t>
+          <t>860ae</t>
         </is>
       </c>
       <c r="I111" s="7" t="n">
@@ -5995,14 +5995,14 @@
         <v>49425</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3837</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>2242749672</v>
+        <v>1.19e+30</v>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>2.24b</t>
+          <t>1.19af</t>
         </is>
       </c>
       <c r="I112" s="7" t="n">
@@ -6044,14 +6044,14 @@
         <v>51065</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1.08</v>
+        <v>1.6807</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>2422169646</v>
+        <v>2e+30</v>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>2.42b</t>
+          <t>2af</t>
         </is>
       </c>
       <c r="I113" s="7" t="n">
@@ -6093,14 +6093,14 @@
         <v>52745</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2615943218</v>
+        <v>2.06e+30</v>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>2.61b</t>
+          <t>2.06af</t>
         </is>
       </c>
       <c r="I114" s="7" t="n">
@@ -6142,14 +6142,14 @@
         <v>54470</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1.08</v>
+        <v>1.4126</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2825218675</v>
+        <v>2.91e+30</v>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>2.82b</t>
+          <t>2.91af</t>
         </is>
       </c>
       <c r="I115" s="7" t="n">
@@ -6191,14 +6191,14 @@
         <v>56235</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1.08</v>
+        <v>1.2715</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>3051236169</v>
+        <v>3.7e+30</v>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>3.05b</t>
+          <t>3.7af</t>
         </is>
       </c>
       <c r="I116" s="7" t="n">
@@ -6240,14 +6240,14 @@
         <v>58045</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1.08</v>
+        <v>1.2486</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>3295335063</v>
+        <v>4.62e+30</v>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>3.29b</t>
+          <t>4.62af</t>
         </is>
       </c>
       <c r="I117" s="7" t="n">
@@ -6289,14 +6289,14 @@
         <v>59900</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1.08</v>
+        <v>1.2381</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>3558961868</v>
+        <v>5.72e+30</v>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>3.55b</t>
+          <t>5.72af</t>
         </is>
       </c>
       <c r="I118" s="7" t="n">
@@ -6338,14 +6338,14 @@
         <v>61805</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3881</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>3843678817</v>
+        <v>7.94e+30</v>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>3.84b</t>
+          <t>7.94af</t>
         </is>
       </c>
       <c r="I119" s="7" t="n">
@@ -6387,14 +6387,14 @@
         <v>63755</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3098</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>4151173122</v>
+        <v>1.04e+31</v>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>4.15b</t>
+          <t>10.3af</t>
         </is>
       </c>
       <c r="I120" s="7" t="n">
@@ -6436,14 +6436,14 @@
         <v>65755</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1.08</v>
+        <v>1.4712</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>4483266972</v>
+        <v>1.53e+31</v>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>4.48b</t>
+          <t>15.3af</t>
         </is>
       </c>
       <c r="I121" s="7" t="n">
@@ -6485,14 +6485,14 @@
         <v>67805</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1.08</v>
+        <v>1.2092</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>4841928330</v>
+        <v>1.85e+31</v>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>4.84b</t>
+          <t>18.5af</t>
         </is>
       </c>
       <c r="I122" s="7" t="n">
@@ -6534,14 +6534,14 @@
         <v>69905</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3838</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>5229282596</v>
+        <v>2.56e+31</v>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>5.22b</t>
+          <t>25.5af</t>
         </is>
       </c>
       <c r="I123" s="7" t="n">
@@ -6583,14 +6583,14 @@
         <v>72060</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3086</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>5647625204</v>
+        <v>3.35e+31</v>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>5.64b</t>
+          <t>33.5af</t>
         </is>
       </c>
       <c r="I124" s="7" t="n">
@@ -6632,14 +6632,14 @@
         <v>74265</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1.08</v>
+        <v>1.4448</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>6099435220</v>
+        <v>4.84e+31</v>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>6.09b</t>
+          <t>48.4af</t>
         </is>
       </c>
       <c r="I125" s="7" t="n">
@@ -6681,14 +6681,14 @@
         <v>76525</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3099</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>6587390038</v>
+        <v>6.34e+31</v>
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>6.58b</t>
+          <t>63.3af</t>
         </is>
       </c>
       <c r="I126" s="7" t="n">
@@ -6730,14 +6730,14 @@
         <v>78845</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3943</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>7114381241</v>
+        <v>8.84e+31</v>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>7.11b</t>
+          <t>88.4af</t>
         </is>
       </c>
       <c r="I127" s="7" t="n">
@@ -6779,14 +6779,14 @@
         <v>81220</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3348</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>7683531740</v>
+        <v>1.18e+32</v>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>7.68b</t>
+          <t>118af</t>
         </is>
       </c>
       <c r="I128" s="7" t="n">
@@ -6828,14 +6828,14 @@
         <v>83655</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1.08</v>
+        <v>2.5169</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>8298214279</v>
+        <v>2.97e+32</v>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>8.29b</t>
+          <t>297af</t>
         </is>
       </c>
       <c r="I129" s="7" t="n">
@@ -6877,14 +6877,14 @@
         <v>86150</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0168</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>8962071422</v>
+        <v>3.02e+32</v>
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>8.96b</t>
+          <t>302af</t>
         </is>
       </c>
       <c r="I130" s="7" t="n">
@@ -6926,14 +6926,14 @@
         <v>88710</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0166</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>9679037136</v>
+        <v>3.07e+32</v>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>9.67b</t>
+          <t>307af</t>
         </is>
       </c>
       <c r="I131" s="7" t="n">
@@ -6975,14 +6975,14 @@
         <v>91335</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0195</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>10453360106</v>
+        <v>3.13e+32</v>
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>10.4b</t>
+          <t>313af</t>
         </is>
       </c>
       <c r="I132" s="7" t="n">
@@ -7024,14 +7024,14 @@
         <v>94025</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1.08</v>
+        <v>1.6358</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>11289628915</v>
+        <v>5.12e+32</v>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>11.2b</t>
+          <t>512af</t>
         </is>
       </c>
       <c r="I133" s="7" t="n">
@@ -7073,14 +7073,14 @@
         <v>96780</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0293</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>12192799228</v>
+        <v>5.27e+32</v>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>12.1b</t>
+          <t>527af</t>
         </is>
       </c>
       <c r="I134" s="7" t="n">
@@ -7122,14 +7122,14 @@
         <v>99605</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3074</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>13168223166</v>
+        <v>6.889999999999999e+32</v>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>13.1b</t>
+          <t>688af</t>
         </is>
       </c>
       <c r="I135" s="7" t="n">
@@ -7171,14 +7171,14 @@
         <v>102500</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3309</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>14221681020</v>
+        <v>9.169999999999999e+32</v>
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>14.2b</t>
+          <t>916af</t>
         </is>
       </c>
       <c r="I136" s="7" t="n">
@@ -7220,14 +7220,14 @@
         <v>105465</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3522</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>15359415501</v>
+        <v>1.24e+33</v>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>15.3b</t>
+          <t>1.24ag</t>
         </is>
       </c>
       <c r="I137" s="7" t="n">
@@ -7269,14 +7269,14 @@
         <v>108505</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3468</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>16588168741</v>
+        <v>1.67e+33</v>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>16.5b</t>
+          <t>1.67ag</t>
         </is>
       </c>
       <c r="I138" s="7" t="n">
@@ -7318,14 +7318,14 @@
         <v>111625</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1.08</v>
+        <v>1.4012</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>17915222241</v>
+        <v>2.34e+33</v>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>17.9b</t>
+          <t>2.34ag</t>
         </is>
       </c>
       <c r="I139" s="7" t="n">
@@ -7367,14 +7367,14 @@
         <v>114820</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3162</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>19348440020</v>
+        <v>3.08e+33</v>
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>19.3b</t>
+          <t>3.08ag</t>
         </is>
       </c>
       <c r="I140" s="7" t="n">
@@ -7416,14 +7416,14 @@
         <v>118095</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1.08</v>
+        <v>1.8247</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>20896315221</v>
+        <v>5.62e+33</v>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>20.8b</t>
+          <t>5.62ag</t>
         </is>
       </c>
       <c r="I141" s="7" t="n">
@@ -7465,14 +7465,14 @@
         <v>121450</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0249</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>22568020439</v>
+        <v>5.76e+33</v>
       </c>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>22.5b</t>
+          <t>5.76ag</t>
         </is>
       </c>
       <c r="I142" s="7" t="n">
@@ -7514,14 +7514,14 @@
         <v>124890</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1.08</v>
+        <v>1.191</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>24373462074</v>
+        <v>6.86e+33</v>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>24.3b</t>
+          <t>6.86ag</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
@@ -7563,14 +7563,14 @@
         <v>128415</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3761</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>26323339040</v>
+        <v>9.439999999999999e+33</v>
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>26.3b</t>
+          <t>9.44ag</t>
         </is>
       </c>
       <c r="I144" s="7" t="n">
@@ -7612,14 +7612,14 @@
         <v>132030</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1.08</v>
+        <v>1.4831</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>28429206163</v>
+        <v>1.4e+34</v>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>28.4b</t>
+          <t>14ag</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
@@ -7661,14 +7661,14 @@
         <v>135735</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1.08</v>
+        <v>1.1857</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>30703542657</v>
+        <v>1.66e+34</v>
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>30.7b</t>
+          <t>16.6ag</t>
         </is>
       </c>
       <c r="I146" s="7" t="n">
@@ -7710,14 +7710,14 @@
         <v>139535</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3434</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>33159826069</v>
+        <v>2.23e+34</v>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>33.1b</t>
+          <t>22.3ag</t>
         </is>
       </c>
       <c r="I147" s="7" t="n">
@@ -7759,14 +7759,14 @@
         <v>143430</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3857</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>35812612155</v>
+        <v>3.09e+34</v>
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>35.8b</t>
+          <t>30.9ag</t>
         </is>
       </c>
       <c r="I148" s="7" t="n">
@@ -7808,14 +7808,14 @@
         <v>147420</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1.08</v>
+        <v>1.4951</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>38677621127</v>
+        <v>4.62e+34</v>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>38.6b</t>
+          <t>46.1ag</t>
         </is>
       </c>
       <c r="I149" s="7" t="n">
@@ -7857,14 +7857,14 @@
         <v>151510</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1.08</v>
+        <v>1.2403</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>41771830817</v>
+        <v>5.73e+34</v>
       </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>41.7b</t>
+          <t>57.3ag</t>
         </is>
       </c>
       <c r="I150" s="7" t="n">
@@ -7906,14 +7906,14 @@
         <v>155705</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>1.08</v>
+        <v>1.3874</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>45113577282</v>
+        <v>7.95e+34</v>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>45.1b</t>
+          <t>79.5ag</t>
         </is>
       </c>
       <c r="I151" s="7" t="n">

--- a/Kachi_Gun/Table/Weapon_Enchant.xlsx
+++ b/Kachi_Gun/Table/Weapon_Enchant.xlsx
@@ -608,11 +608,11 @@
         <v>1</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>46200</v>
+        <v>36200</v>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>46.2k</t>
+          <t>36.2k</t>
         </is>
       </c>
       <c r="I2" s="7" t="n">
@@ -654,14 +654,14 @@
         <v>40</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>11.9264</v>
+        <v>14.4751</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>551000</v>
+        <v>524000</v>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>551k</t>
+          <t>524k</t>
         </is>
       </c>
       <c r="I3" s="7" t="n">
@@ -703,14 +703,14 @@
         <v>60</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3.0853</v>
+        <v>2.8435</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1700000</v>
+        <v>1490000</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>1.7m</t>
+          <t>1.49m</t>
         </is>
       </c>
       <c r="I4" s="7" t="n">
@@ -752,14 +752,14 @@
         <v>85</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2.1471</v>
+        <v>3.7785</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>3650000</v>
+        <v>5630000</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>3.65m</t>
+          <t>5.63m</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
@@ -801,14 +801,14 @@
         <v>110</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.2055</v>
+        <v>1.6075</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>19000000</v>
+        <v>9050000</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>19m</t>
+          <t>9.05m</t>
         </is>
       </c>
       <c r="I6" s="7" t="n">
@@ -850,14 +850,14 @@
         <v>135</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.0158</v>
+        <v>7.5691</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>76300000</v>
+        <v>68500000</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>76.3m</t>
+          <t>68.5m</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -899,14 +899,14 @@
         <v>160</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.8663</v>
+        <v>5.8686</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>295000000</v>
+        <v>402000000</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>295m</t>
+          <t>402m</t>
         </is>
       </c>
       <c r="I8" s="7" t="n">
@@ -948,14 +948,14 @@
         <v>190</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.4068</v>
+        <v>2.8358</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1890000000</v>
+        <v>1140000000</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>1.89b</t>
+          <t>1.13b</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">
@@ -997,14 +997,14 @@
         <v>220</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.0159</v>
+        <v>2.7456</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>3810000000</v>
+        <v>3130000000</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>3.81b</t>
+          <t>3.13b</t>
         </is>
       </c>
       <c r="I10" s="7" t="n">
@@ -1046,14 +1046,14 @@
         <v>250</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.3071</v>
+        <v>2.7316</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>12600000000</v>
+        <v>8550000000</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>12.6b</t>
+          <t>8.55b</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
@@ -1095,14 +1095,14 @@
         <v>285</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.6349</v>
+        <v>2.5965</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>20600000000</v>
+        <v>22200000000</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>20.6b</t>
+          <t>22.2b</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
@@ -1144,14 +1144,14 @@
         <v>320</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.4515</v>
+        <v>3.0045</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>71100000000</v>
+        <v>66700000000</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>71.1b</t>
+          <t>66.7b</t>
         </is>
       </c>
       <c r="I13" s="7" t="n">
@@ -1193,14 +1193,14 @@
         <v>355</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.3066</v>
+        <v>1.06</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>92900000000</v>
+        <v>70700000000</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>92.9b</t>
+          <t>70.7b</t>
         </is>
       </c>
       <c r="I14" s="7" t="n">
@@ -1242,14 +1242,14 @@
         <v>395</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.6491</v>
+        <v>2.5743</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>339000000000</v>
+        <v>182000000000</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>339b</t>
+          <t>182b</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
@@ -1291,14 +1291,14 @@
         <v>435</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.4867</v>
+        <v>2.6484</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>504000000000</v>
+        <v>482000000000</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>504b</t>
+          <t>482b</t>
         </is>
       </c>
       <c r="I16" s="7" t="n">
@@ -1340,14 +1340,14 @@
         <v>475</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.7103</v>
+        <v>2.1992</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1870000000000</v>
+        <v>1060000000000</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>1.87t</t>
+          <t>1.06t</t>
         </is>
       </c>
       <c r="I17" s="7" t="n">
@@ -1389,14 +1389,14 @@
         <v>520</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.5561</v>
+        <v>2.5755</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2910000000000</v>
+        <v>2730000000000</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>2.91t</t>
+          <t>2.73t</t>
         </is>
       </c>
       <c r="I18" s="7" t="n">
@@ -1438,14 +1438,14 @@
         <v>565</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.5361</v>
+        <v>2.0513</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>13200000000000</v>
+        <v>5600000000000</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>13.2t</t>
+          <t>5.6t</t>
         </is>
       </c>
       <c r="I19" s="7" t="n">
@@ -1487,14 +1487,14 @@
         <v>615</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.1515</v>
+        <v>2.6786</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>15200000000000</v>
+        <v>15000000000000</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>15.2t</t>
+          <t>15t</t>
         </is>
       </c>
       <c r="I20" s="7" t="n">
@@ -1536,14 +1536,14 @@
         <v>665</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.8684</v>
+        <v>1.4133</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>58800000000000</v>
+        <v>21200000000000</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>58.8t</t>
+          <t>21.2t</t>
         </is>
       </c>
       <c r="I21" s="7" t="n">
@@ -1585,14 +1585,14 @@
         <v>720</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.0068</v>
+        <v>2.5377</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>59200000000000</v>
+        <v>53800000000000</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>59.2t</t>
+          <t>53.8t</t>
         </is>
       </c>
       <c r="I22" s="7" t="n">
@@ -1634,14 +1634,14 @@
         <v>775</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.1791</v>
+        <v>3.5688</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>129000000000000</v>
+        <v>192000000000000</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>129t</t>
+          <t>192t</t>
         </is>
       </c>
       <c r="I23" s="7" t="n">
@@ -1683,14 +1683,14 @@
         <v>835</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.3721</v>
+        <v>1.4844</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>306000000000000</v>
+        <v>285000000000000</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>306t</t>
+          <t>285t</t>
         </is>
       </c>
       <c r="I24" s="7" t="n">
@@ -1732,14 +1732,14 @@
         <v>895</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.1569</v>
+        <v>3.1228</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>660000000000000</v>
+        <v>890000000000000</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>660t</t>
+          <t>890t</t>
         </is>
       </c>
       <c r="I25" s="7" t="n">
@@ -1781,14 +1781,14 @@
         <v>960</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.3788</v>
+        <v>1.8764</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1570000000000000</v>
+        <v>1670000000000000</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>1.57aa</t>
+          <t>1.67aa</t>
         </is>
       </c>
       <c r="I26" s="7" t="n">
@@ -1830,14 +1830,14 @@
         <v>1030</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.3248</v>
+        <v>2.1677</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>5220000000000000</v>
+        <v>3620000000000000</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>5.22aa</t>
+          <t>3.62aa</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
@@ -1879,14 +1879,14 @@
         <v>1100</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.2395</v>
+        <v>3.895</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>6470000000000000</v>
+        <v>1.41e+16</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>6.47aa</t>
+          <t>14.1aa</t>
         </is>
       </c>
       <c r="I28" s="7" t="n">
@@ -1928,14 +1928,14 @@
         <v>1175</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.7156</v>
+        <v>0.9858</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1.11e+16</v>
+        <v>1.39e+16</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>11.1aa</t>
+          <t>13.9aa</t>
         </is>
       </c>
       <c r="I29" s="7" t="n">
@@ -1977,14 +1977,14 @@
         <v>1255</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.8919</v>
+        <v>1.2662</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>2.1e+16</v>
+        <v>1.76e+16</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>21aa</t>
+          <t>17.6aa</t>
         </is>
       </c>
       <c r="I30" s="7" t="n">
@@ -2026,14 +2026,14 @@
         <v>1335</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.7952</v>
+        <v>1.8239</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>3.77e+16</v>
+        <v>3.21e+16</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>37.7aa</t>
+          <t>32.1aa</t>
         </is>
       </c>
       <c r="I31" s="7" t="n">
@@ -2075,14 +2075,14 @@
         <v>1420</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.5756</v>
+        <v>1.5545</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>5.94e+16</v>
+        <v>4.99e+16</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>59.4aa</t>
+          <t>49.9aa</t>
         </is>
       </c>
       <c r="I32" s="7" t="n">
@@ -2124,14 +2124,14 @@
         <v>1510</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.8687</v>
+        <v>1.6112</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1.11e+17</v>
+        <v>8.04e+16</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>111aa</t>
+          <t>80.4aa</t>
         </is>
       </c>
       <c r="I33" s="7" t="n">
@@ -2173,14 +2173,14 @@
         <v>1605</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.8108</v>
+        <v>2.7736</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>2.01e+17</v>
+        <v>2.23e+17</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>201aa</t>
+          <t>223aa</t>
         </is>
       </c>
       <c r="I34" s="7" t="n">
@@ -2222,14 +2222,14 @@
         <v>1705</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.806</v>
+        <v>1.2556</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>3.63e+17</v>
+        <v>2.8e+17</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>363aa</t>
+          <t>280aa</t>
         </is>
       </c>
       <c r="I35" s="7" t="n">
@@ -2271,14 +2271,14 @@
         <v>1810</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1.6749</v>
+        <v>2.6286</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>6.08e+17</v>
+        <v>7.36e+17</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>608aa</t>
+          <t>736aa</t>
         </is>
       </c>
       <c r="I36" s="7" t="n">
@@ -2320,14 +2320,14 @@
         <v>1920</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.7434</v>
+        <v>1.3546</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.06e+18</v>
+        <v>9.97e+17</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>1.06ab</t>
+          <t>997aa</t>
         </is>
       </c>
       <c r="I37" s="7" t="n">
@@ -2369,14 +2369,14 @@
         <v>2035</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2.3019</v>
+        <v>1.5346</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>2.44e+18</v>
+        <v>1.53e+18</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>2.44ab</t>
+          <t>1.53ab</t>
         </is>
       </c>
       <c r="I38" s="7" t="n">
@@ -2418,14 +2418,14 @@
         <v>2155</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.582</v>
+        <v>2.2549</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>3.86e+18</v>
+        <v>3.45e+18</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>3.86ab</t>
+          <t>3.45ab</t>
         </is>
       </c>
       <c r="I39" s="7" t="n">
@@ -2467,14 +2467,14 @@
         <v>2285</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1.8238</v>
+        <v>1.4725</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>7.04e+18</v>
+        <v>5.08e+18</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>7.04ab</t>
+          <t>5.08ab</t>
         </is>
       </c>
       <c r="I40" s="7" t="n">
@@ -2516,14 +2516,14 @@
         <v>2420</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1.9176</v>
+        <v>2.3031</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.35e+19</v>
+        <v>1.17e+19</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>13.5ab</t>
+          <t>11.7ab</t>
         </is>
       </c>
       <c r="I41" s="7" t="n">
@@ -2565,14 +2565,14 @@
         <v>2560</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.5185</v>
+        <v>1.2991</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>2.05e+19</v>
+        <v>1.52e+19</v>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>20.5ab</t>
+          <t>15.2ab</t>
         </is>
       </c>
       <c r="I42" s="7" t="n">
@@ -2614,14 +2614,14 @@
         <v>2710</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1.8049</v>
+        <v>1.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>3.7e+19</v>
+        <v>2.66e+19</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>37ab</t>
+          <t>26.6ab</t>
         </is>
       </c>
       <c r="I43" s="7" t="n">
@@ -2663,14 +2663,14 @@
         <v>2865</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1.9486</v>
+        <v>1.8308</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>7.21e+19</v>
+        <v>4.87e+19</v>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>72.1ab</t>
+          <t>48.7ab</t>
         </is>
       </c>
       <c r="I44" s="7" t="n">
@@ -2712,14 +2712,14 @@
         <v>3030</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1.595</v>
+        <v>1.9261</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.15e+20</v>
+        <v>9.38e+19</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>115ab</t>
+          <t>93.8ab</t>
         </is>
       </c>
       <c r="I45" s="7" t="n">
@@ -2761,14 +2761,14 @@
         <v>3200</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2.0957</v>
+        <v>1.5352</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2.41e+20</v>
+        <v>1.44e+20</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>241ab</t>
+          <t>144ab</t>
         </is>
       </c>
       <c r="I46" s="7" t="n">
@@ -2810,14 +2810,14 @@
         <v>3380</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.6515</v>
+        <v>1.4444</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>3.98e+20</v>
+        <v>2.08e+20</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>398ab</t>
+          <t>208ab</t>
         </is>
       </c>
       <c r="I47" s="7" t="n">
@@ -2859,14 +2859,14 @@
         <v>3570</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2.005</v>
+        <v>1.7596</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>7.98e+20</v>
+        <v>3.66e+20</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>798ab</t>
+          <t>366ab</t>
         </is>
       </c>
       <c r="I48" s="7" t="n">
@@ -2908,14 +2908,14 @@
         <v>3770</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.3283</v>
+        <v>4.6995</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1.06e+21</v>
+        <v>1.72e+21</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>1.06ac</t>
+          <t>1.72ac</t>
         </is>
       </c>
       <c r="I49" s="7" t="n">
@@ -2957,14 +2957,14 @@
         <v>3980</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3.0755</v>
+        <v>1.6802</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>3.26e+21</v>
+        <v>2.89e+21</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>3.26ac</t>
+          <t>2.89ac</t>
         </is>
       </c>
       <c r="I50" s="7" t="n">
@@ -3006,14 +3006,14 @@
         <v>4200</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1.0368</v>
+        <v>1.0934</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>3.38e+21</v>
+        <v>3.16e+21</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>3.38ac</t>
+          <t>3.16ac</t>
         </is>
       </c>
       <c r="I51" s="7" t="n">
@@ -3055,14 +3055,14 @@
         <v>4425</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2.3402</v>
+        <v>1.0696</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>7.910000000000001e+21</v>
+        <v>3.38e+21</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>7.91ac</t>
+          <t>3.38ac</t>
         </is>
       </c>
       <c r="I52" s="7" t="n">
@@ -3104,14 +3104,14 @@
         <v>4660</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1.0202</v>
+        <v>1.0799</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>8.070000000000001e+21</v>
+        <v>3.65e+21</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>8.07ac</t>
+          <t>3.65ac</t>
         </is>
       </c>
       <c r="I53" s="7" t="n">
@@ -3153,14 +3153,14 @@
         <v>4900</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1.0248</v>
+        <v>1.3671</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>8.270000000000001e+21</v>
+        <v>4.990000000000001e+21</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>8.27ac</t>
+          <t>4.99ac</t>
         </is>
       </c>
       <c r="I54" s="7" t="n">
@@ -3202,14 +3202,14 @@
         <v>5150</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.9347</v>
+        <v>1.4068</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.6e+22</v>
+        <v>7.02e+21</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>16ac</t>
+          <t>7.02ac</t>
         </is>
       </c>
       <c r="I55" s="7" t="n">
@@ -3251,14 +3251,14 @@
         <v>5410</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1.1188</v>
+        <v>1.7236</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>1.79e+22</v>
+        <v>1.21e+22</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>17.9ac</t>
+          <t>12.1ac</t>
         </is>
       </c>
       <c r="I56" s="7" t="n">
@@ -3300,14 +3300,14 @@
         <v>5680</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1.2682</v>
+        <v>1.0413</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2.27e+22</v>
+        <v>1.26e+22</v>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>22.7ac</t>
+          <t>12.6ac</t>
         </is>
       </c>
       <c r="I57" s="7" t="n">
@@ -3349,14 +3349,14 @@
         <v>5960</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1.4185</v>
+        <v>1.4365</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>3.22e+22</v>
+        <v>1.81e+22</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>32.1ac</t>
+          <t>18ac</t>
         </is>
       </c>
       <c r="I58" s="7" t="n">
@@ -3398,14 +3398,14 @@
         <v>6250</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2.5124</v>
+        <v>1.4862</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>8.090000000000001e+22</v>
+        <v>2.69e+22</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>80.9ac</t>
+          <t>26.9ac</t>
         </is>
       </c>
       <c r="I59" s="7" t="n">
@@ -3447,14 +3447,14 @@
         <v>6550</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1.0161</v>
+        <v>1.4126</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>8.219999999999999e+22</v>
+        <v>3.8e+22</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>82.1ac</t>
+          <t>38ac</t>
         </is>
       </c>
       <c r="I60" s="7" t="n">
@@ -3496,14 +3496,14 @@
         <v>6860</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1.399</v>
+        <v>3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1.15e+23</v>
+        <v>1.14e+23</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>115ac</t>
+          <t>114ac</t>
         </is>
       </c>
       <c r="I61" s="7" t="n">
@@ -3545,14 +3545,14 @@
         <v>7180</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1.0261</v>
+        <v>1.0702</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1.18e+23</v>
+        <v>1.22e+23</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>118ac</t>
+          <t>122ac</t>
         </is>
       </c>
       <c r="I62" s="7" t="n">
@@ -3594,14 +3594,14 @@
         <v>7510</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2.4915</v>
+        <v>1.0574</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2.94e+23</v>
+        <v>1.29e+23</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>294ac</t>
+          <t>129ac</t>
         </is>
       </c>
       <c r="I63" s="7" t="n">
@@ -3643,14 +3643,14 @@
         <v>7850</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1.0306</v>
+        <v>1.0698</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>3.03e+23</v>
+        <v>1.38e+23</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>303ac</t>
+          <t>138ac</t>
         </is>
       </c>
       <c r="I64" s="7" t="n">
@@ -3692,14 +3692,14 @@
         <v>8205</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.0363</v>
+        <v>1.4565</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>3.14e+23</v>
+        <v>2.01e+23</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>314ac</t>
+          <t>201ac</t>
         </is>
       </c>
       <c r="I65" s="7" t="n">
@@ -3741,14 +3741,14 @@
         <v>8570</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1.3057</v>
+        <v>1.8259</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>4.1e+23</v>
+        <v>3.67e+23</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>410ac</t>
+          <t>367ac</t>
         </is>
       </c>
       <c r="I66" s="7" t="n">
@@ -3790,14 +3790,14 @@
         <v>8950</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1.5561</v>
+        <v>1.4632</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>6.38e+23</v>
+        <v>5.37e+23</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>638ac</t>
+          <t>537ac</t>
         </is>
       </c>
       <c r="I67" s="7" t="n">
@@ -3839,14 +3839,14 @@
         <v>9340</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1.2539</v>
+        <v>1.0708</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>7.999999999999999e+23</v>
+        <v>5.75e+23</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>799ac</t>
+          <t>575ac</t>
         </is>
       </c>
       <c r="I68" s="7" t="n">
@@ -3888,14 +3888,14 @@
         <v>9745</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1.45</v>
+        <v>1.3948</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>1.16e+24</v>
+        <v>8.02e+23</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>1.16ad</t>
+          <t>802ac</t>
         </is>
       </c>
       <c r="I69" s="7" t="n">
@@ -3937,14 +3937,14 @@
         <v>10165</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2.7672</v>
+        <v>1.5212</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>3.21e+24</v>
+        <v>1.22e+24</v>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>3.21ad</t>
+          <t>1.22ad</t>
         </is>
       </c>
       <c r="I70" s="7" t="n">
@@ -3986,14 +3986,14 @@
         <v>10600</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.0218</v>
+        <v>1.2541</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3.28e+24</v>
+        <v>1.53e+24</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>3.28ad</t>
+          <t>1.53ad</t>
         </is>
       </c>
       <c r="I71" s="7" t="n">
@@ -4035,14 +4035,14 @@
         <v>11050</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1.0274</v>
+        <v>1.4641</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>3.37e+24</v>
+        <v>2.24e+24</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>3.37ad</t>
+          <t>2.24ad</t>
         </is>
       </c>
       <c r="I72" s="7" t="n">
@@ -4084,14 +4084,14 @@
         <v>11515</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1.4154</v>
+        <v>1.4241</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>4.77e+24</v>
+        <v>3.19e+24</v>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>4.77ad</t>
+          <t>3.19ad</t>
         </is>
       </c>
       <c r="I73" s="7" t="n">
@@ -4133,14 +4133,14 @@
         <v>11995</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1.2516</v>
+        <v>1.3605</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>5.97e+24</v>
+        <v>4.34e+24</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>5.97ad</t>
+          <t>4.34ad</t>
         </is>
       </c>
       <c r="I74" s="7" t="n">
@@ -4182,14 +4182,14 @@
         <v>12495</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1.8928</v>
+        <v>1.3917</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1.13e+25</v>
+        <v>6.04e+24</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>11.3ad</t>
+          <t>6.04ad</t>
         </is>
       </c>
       <c r="I75" s="7" t="n">
@@ -4231,14 +4231,14 @@
         <v>13010</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.0442</v>
+        <v>2.5828</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1.18e+25</v>
+        <v>1.56e+25</v>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>11.7ad</t>
+          <t>15.6ad</t>
         </is>
       </c>
       <c r="I76" s="7" t="n">
@@ -4280,14 +4280,14 @@
         <v>13545</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1.3644</v>
+        <v>1.0256</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1.61e+25</v>
+        <v>1.6e+25</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>16.1ad</t>
+          <t>16ad</t>
         </is>
       </c>
       <c r="I77" s="7" t="n">
@@ -4329,14 +4329,14 @@
         <v>14100</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1.323</v>
+        <v>1.0438</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>2.13e+25</v>
+        <v>1.67e+25</v>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>21.3ad</t>
+          <t>16.7ad</t>
         </is>
       </c>
       <c r="I78" s="7" t="n">
@@ -4378,14 +4378,14 @@
         <v>14670</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1.6244</v>
+        <v>1.4251</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>3.46e+25</v>
+        <v>2.38e+25</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>34.6ad</t>
+          <t>23.8ad</t>
         </is>
       </c>
       <c r="I79" s="7" t="n">
@@ -4427,14 +4427,14 @@
         <v>15260</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1.2486</v>
+        <v>1.4202</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>4.32e+25</v>
+        <v>3.38e+25</v>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>43.2ad</t>
+          <t>33.8ad</t>
         </is>
       </c>
       <c r="I80" s="7" t="n">
@@ -4476,14 +4476,14 @@
         <v>15875</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1.4375</v>
+        <v>1.568</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>6.21e+25</v>
+        <v>5.3e+25</v>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>62.1ad</t>
+          <t>53ad</t>
         </is>
       </c>
       <c r="I81" s="7" t="n">
@@ -4525,14 +4525,14 @@
         <v>16510</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.4976</v>
+        <v>1.2623</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>9.3e+25</v>
+        <v>6.69e+25</v>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>93ad</t>
+          <t>66.9ad</t>
         </is>
       </c>
       <c r="I82" s="7" t="n">
@@ -4574,14 +4574,14 @@
         <v>17165</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2.0538</v>
+        <v>1.3558</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1.91e+26</v>
+        <v>9.07e+25</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>191ad</t>
+          <t>90.7ad</t>
         </is>
       </c>
       <c r="I83" s="7" t="n">
@@ -4623,14 +4623,14 @@
         <v>17845</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1.0105</v>
+        <v>1.3671</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1.93e+26</v>
+        <v>1.24e+26</v>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>193ad</t>
+          <t>124ad</t>
         </is>
       </c>
       <c r="I84" s="7" t="n">
@@ -4672,14 +4672,14 @@
         <v>18550</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1.3938</v>
+        <v>1.4194</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>2.69e+26</v>
+        <v>1.76e+26</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>269ad</t>
+          <t>176ad</t>
         </is>
       </c>
       <c r="I85" s="7" t="n">
@@ -4721,14 +4721,14 @@
         <v>19280</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1.6952</v>
+        <v>1.4091</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>4.56e+26</v>
+        <v>2.48e+26</v>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>456ad</t>
+          <t>248ad</t>
         </is>
       </c>
       <c r="I86" s="7" t="n">
@@ -4770,14 +4770,14 @@
         <v>20035</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1.0285</v>
+        <v>1.4718</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>4.69e+26</v>
+        <v>3.65e+26</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>469ad</t>
+          <t>365ad</t>
         </is>
       </c>
       <c r="I87" s="7" t="n">
@@ -4819,14 +4819,14 @@
         <v>20815</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1.3412</v>
+        <v>1.5945</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>6.29e+26</v>
+        <v>5.82e+26</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>629ad</t>
+          <t>582ad</t>
         </is>
       </c>
       <c r="I88" s="7" t="n">
@@ -4868,14 +4868,14 @@
         <v>21620</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1.496</v>
+        <v>1.4192</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>9.41e+26</v>
+        <v>8.26e+26</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>941ad</t>
+          <t>826ad</t>
         </is>
       </c>
       <c r="I89" s="7" t="n">
@@ -4917,14 +4917,14 @@
         <v>22455</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1.3496</v>
+        <v>2.046</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1.27e+27</v>
+        <v>1.69e+27</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>1.26ae</t>
+          <t>1.69ae</t>
         </is>
       </c>
       <c r="I90" s="7" t="n">
@@ -4966,14 +4966,14 @@
         <v>23320</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1.4961</v>
+        <v>1.3964</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1.9e+27</v>
+        <v>2.36e+27</v>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>1.9ae</t>
+          <t>2.36ae</t>
         </is>
       </c>
       <c r="I91" s="7" t="n">
@@ -5015,14 +5015,14 @@
         <v>24215</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1.4211</v>
+        <v>1.0212</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>2.7e+27</v>
+        <v>2.41e+27</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>2.7ae</t>
+          <t>2.4ae</t>
         </is>
       </c>
       <c r="I92" s="7" t="n">
@@ -5064,14 +5064,14 @@
         <v>25140</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1.4593</v>
+        <v>1.3029</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>3.94e+27</v>
+        <v>3.14e+27</v>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>3.94ae</t>
+          <t>3.13ae</t>
         </is>
       </c>
       <c r="I93" s="7" t="n">
@@ -5113,14 +5113,14 @@
         <v>26100</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2.0838</v>
+        <v>1.3822</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>8.21e+27</v>
+        <v>4.34e+27</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>8.21ae</t>
+          <t>4.34ae</t>
         </is>
       </c>
       <c r="I94" s="7" t="n">
@@ -5162,14 +5162,14 @@
         <v>27090</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1.0037</v>
+        <v>1.6728</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>8.24e+27</v>
+        <v>7.26e+27</v>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>8.24ae</t>
+          <t>7.26ae</t>
         </is>
       </c>
       <c r="I95" s="7" t="n">
@@ -5211,14 +5211,14 @@
         <v>28115</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1.25</v>
+        <v>1.219</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1.03e+28</v>
+        <v>8.85e+27</v>
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>10.2ae</t>
+          <t>8.85ae</t>
         </is>
       </c>
       <c r="I96" s="7" t="n">
@@ -5260,14 +5260,14 @@
         <v>29180</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2.165</v>
+        <v>1.5593</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>2.23e+28</v>
+        <v>1.38e+28</v>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>22.3ae</t>
+          <t>13.8ae</t>
         </is>
       </c>
       <c r="I97" s="7" t="n">
@@ -5309,14 +5309,14 @@
         <v>30280</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1.0135</v>
+        <v>1.2319</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>2.26e+28</v>
+        <v>1.7e+28</v>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>22.6ae</t>
+          <t>17ae</t>
         </is>
       </c>
       <c r="I98" s="7" t="n">
@@ -5358,14 +5358,14 @@
         <v>31420</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1.2124</v>
+        <v>1.4824</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>2.74e+28</v>
+        <v>2.52e+28</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>27.4ae</t>
+          <t>25.2ae</t>
         </is>
       </c>
       <c r="I99" s="7" t="n">
@@ -5407,14 +5407,14 @@
         <v>32600</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1.3942</v>
+        <v>1.4048</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>3.82e+28</v>
+        <v>3.54e+28</v>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>38.2ae</t>
+          <t>35.4ae</t>
         </is>
       </c>
       <c r="I100" s="7" t="n">
@@ -5456,14 +5456,14 @@
         <v>33820</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1.4188</v>
+        <v>1.5395</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>5.42e+28</v>
+        <v>5.45e+28</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>54.2ae</t>
+          <t>54.5ae</t>
         </is>
       </c>
       <c r="I101" s="7" t="n">
@@ -5505,14 +5505,14 @@
         <v>35070</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1.4668</v>
+        <v>1.5303</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>7.95e+28</v>
+        <v>8.339999999999999e+28</v>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>79.5ae</t>
+          <t>83.3ae</t>
         </is>
       </c>
       <c r="I102" s="7" t="n">
@@ -5554,14 +5554,14 @@
         <v>36350</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1.4214</v>
+        <v>1.3789</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.13e+29</v>
+        <v>1.15e+29</v>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>113ae</t>
+          <t>115ae</t>
         </is>
       </c>
       <c r="I103" s="7" t="n">
@@ -5603,14 +5603,14 @@
         <v>37665</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1.2832</v>
+        <v>2.2435</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1.45e+29</v>
+        <v>2.58e+29</v>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>145ae</t>
+          <t>258ae</t>
         </is>
       </c>
       <c r="I104" s="7" t="n">
@@ -5652,14 +5652,14 @@
         <v>39010</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1.3793</v>
+        <v>1.0116</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>2e+29</v>
+        <v>2.61e+29</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>199ae</t>
+          <t>261ae</t>
         </is>
       </c>
       <c r="I105" s="7" t="n">
@@ -5701,14 +5701,14 @@
         <v>40390</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>2.73</v>
+        <v>1.0153</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>5.46e+29</v>
+        <v>2.65e+29</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>546ae</t>
+          <t>265ae</t>
         </is>
       </c>
       <c r="I106" s="7" t="n">
@@ -5750,14 +5750,14 @@
         <v>41805</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1.011</v>
+        <v>1.0189</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>5.52e+29</v>
+        <v>2.7e+29</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>552ae</t>
+          <t>270ae</t>
         </is>
       </c>
       <c r="I107" s="7" t="n">
@@ -5799,14 +5799,14 @@
         <v>43255</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1.0109</v>
+        <v>1.3444</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>5.58e+29</v>
+        <v>3.63e+29</v>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>558ae</t>
+          <t>362ae</t>
         </is>
       </c>
       <c r="I108" s="7" t="n">
@@ -5848,14 +5848,14 @@
         <v>44740</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1.3853</v>
+        <v>1.3912</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>7.729999999999999e+29</v>
+        <v>5.05e+29</v>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>772ae</t>
+          <t>505ae</t>
         </is>
       </c>
       <c r="I109" s="7" t="n">
@@ -5897,14 +5897,14 @@
         <v>46265</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1.0207</v>
+        <v>1.7901</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>7.889999999999999e+29</v>
+        <v>9.04e+29</v>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>788ae</t>
+          <t>904ae</t>
         </is>
       </c>
       <c r="I110" s="7" t="n">
@@ -5946,14 +5946,14 @@
         <v>47825</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1.09</v>
+        <v>1.031</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>8.600000000000001e+29</v>
+        <v>9.32e+29</v>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>860ae</t>
+          <t>932ae</t>
         </is>
       </c>
       <c r="I111" s="7" t="n">
@@ -5995,14 +5995,14 @@
         <v>49425</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1.3837</v>
+        <v>1.0697</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1.19e+30</v>
+        <v>9.97e+29</v>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>1.19af</t>
+          <t>997ae</t>
         </is>
       </c>
       <c r="I112" s="7" t="n">
@@ -6044,14 +6044,14 @@
         <v>51065</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1.6807</v>
+        <v>1.3139</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>2e+30</v>
+        <v>1.31e+30</v>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>2af</t>
+          <t>1.3af</t>
         </is>
       </c>
       <c r="I113" s="7" t="n">
@@ -6093,14 +6093,14 @@
         <v>52745</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1.03</v>
+        <v>1.3435</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2.06e+30</v>
+        <v>1.76e+30</v>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>2.06af</t>
+          <t>1.76af</t>
         </is>
       </c>
       <c r="I114" s="7" t="n">
@@ -6142,14 +6142,14 @@
         <v>54470</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1.4126</v>
+        <v>1.608</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2.91e+30</v>
+        <v>2.83e+30</v>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>2.91af</t>
+          <t>2.83af</t>
         </is>
       </c>
       <c r="I115" s="7" t="n">
@@ -6191,14 +6191,14 @@
         <v>56235</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1.2715</v>
+        <v>1.106</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>3.7e+30</v>
+        <v>3.13e+30</v>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>3.7af</t>
+          <t>3.13af</t>
         </is>
       </c>
       <c r="I116" s="7" t="n">
@@ -6240,14 +6240,14 @@
         <v>58045</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1.2486</v>
+        <v>1.3482</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>4.62e+30</v>
+        <v>4.22e+30</v>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>4.62af</t>
+          <t>4.22af</t>
         </is>
       </c>
       <c r="I117" s="7" t="n">
@@ -6289,14 +6289,14 @@
         <v>59900</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1.2381</v>
+        <v>1.2891</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>5.72e+30</v>
+        <v>5.44e+30</v>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>5.72af</t>
+          <t>5.44af</t>
         </is>
       </c>
       <c r="I118" s="7" t="n">
@@ -6338,14 +6338,14 @@
         <v>61805</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1.3881</v>
+        <v>1.3585</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>7.94e+30</v>
+        <v>7.389999999999999e+30</v>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>7.94af</t>
+          <t>7.39af</t>
         </is>
       </c>
       <c r="I119" s="7" t="n">
@@ -6387,14 +6387,14 @@
         <v>63755</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1.3098</v>
+        <v>1.318</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>1.04e+31</v>
+        <v>9.74e+30</v>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>10.3af</t>
+          <t>9.74af</t>
         </is>
       </c>
       <c r="I120" s="7" t="n">
@@ -6436,14 +6436,14 @@
         <v>65755</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1.4712</v>
+        <v>1.4066</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1.53e+31</v>
+        <v>1.37e+31</v>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>15.3af</t>
+          <t>13.7af</t>
         </is>
       </c>
       <c r="I121" s="7" t="n">
@@ -6485,14 +6485,14 @@
         <v>67805</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1.2092</v>
+        <v>1.2847</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>1.85e+31</v>
+        <v>1.76e+31</v>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>18.5af</t>
+          <t>17.5af</t>
         </is>
       </c>
       <c r="I122" s="7" t="n">
@@ -6534,14 +6534,14 @@
         <v>69905</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1.3838</v>
+        <v>1.392</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>2.56e+31</v>
+        <v>2.45e+31</v>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>25.5af</t>
+          <t>24.5af</t>
         </is>
       </c>
       <c r="I123" s="7" t="n">
@@ -6583,14 +6583,14 @@
         <v>72060</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1.3086</v>
+        <v>1.3714</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>3.35e+31</v>
+        <v>3.36e+31</v>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>33.5af</t>
+          <t>33.6af</t>
         </is>
       </c>
       <c r="I124" s="7" t="n">
@@ -6632,14 +6632,14 @@
         <v>74265</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1.4448</v>
+        <v>1.378</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>4.84e+31</v>
+        <v>4.63e+31</v>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>48.4af</t>
+          <t>46.3af</t>
         </is>
       </c>
       <c r="I125" s="7" t="n">
@@ -6681,10 +6681,10 @@
         <v>76525</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1.3099</v>
+        <v>1.3672</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>6.34e+31</v>
+        <v>6.33e+31</v>
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
@@ -6730,14 +6730,14 @@
         <v>78845</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1.3943</v>
+        <v>1.3886</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>8.84e+31</v>
+        <v>8.79e+31</v>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>88.4af</t>
+          <t>87.8af</t>
         </is>
       </c>
       <c r="I127" s="7" t="n">
@@ -6779,14 +6779,14 @@
         <v>81220</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1.3348</v>
+        <v>2.3891</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>1.18e+32</v>
+        <v>2.1e+32</v>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>118af</t>
+          <t>210af</t>
         </is>
       </c>
       <c r="I128" s="7" t="n">
@@ -6828,14 +6828,14 @@
         <v>83655</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>2.5169</v>
+        <v>1.0524</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2.97e+32</v>
+        <v>2.21e+32</v>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>297af</t>
+          <t>221af</t>
         </is>
       </c>
       <c r="I129" s="7" t="n">
@@ -6877,14 +6877,14 @@
         <v>86150</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1.0168</v>
+        <v>1.0181</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>3.02e+32</v>
+        <v>2.25e+32</v>
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>302af</t>
+          <t>225af</t>
         </is>
       </c>
       <c r="I130" s="7" t="n">
@@ -6926,14 +6926,14 @@
         <v>88710</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1.0166</v>
+        <v>1.0222</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>3.07e+32</v>
+        <v>2.3e+32</v>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>307af</t>
+          <t>230af</t>
         </is>
       </c>
       <c r="I131" s="7" t="n">
@@ -6975,14 +6975,14 @@
         <v>91335</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1.0195</v>
+        <v>1.213</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>3.13e+32</v>
+        <v>2.79e+32</v>
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>313af</t>
+          <t>279af</t>
         </is>
       </c>
       <c r="I132" s="7" t="n">
@@ -7024,14 +7024,14 @@
         <v>94025</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1.6358</v>
+        <v>1.4194</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>5.12e+32</v>
+        <v>3.96e+32</v>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>512af</t>
+          <t>396af</t>
         </is>
       </c>
       <c r="I133" s="7" t="n">
@@ -7073,14 +7073,14 @@
         <v>96780</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1.0293</v>
+        <v>1.2475</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>5.27e+32</v>
+        <v>4.94e+32</v>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>527af</t>
+          <t>494af</t>
         </is>
       </c>
       <c r="I134" s="7" t="n">
@@ -7122,14 +7122,14 @@
         <v>99605</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1.3074</v>
+        <v>1.3219</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>6.889999999999999e+32</v>
+        <v>6.53e+32</v>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>688af</t>
+          <t>653af</t>
         </is>
       </c>
       <c r="I135" s="7" t="n">
@@ -7171,14 +7171,14 @@
         <v>102500</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1.3309</v>
+        <v>1.317</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>9.169999999999999e+32</v>
+        <v>8.599999999999999e+32</v>
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>916af</t>
+          <t>859af</t>
         </is>
       </c>
       <c r="I136" s="7" t="n">
@@ -7220,14 +7220,14 @@
         <v>105465</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1.3522</v>
+        <v>1.3837</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>1.24e+33</v>
+        <v>1.19e+33</v>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>1.24ag</t>
+          <t>1.19ag</t>
         </is>
       </c>
       <c r="I137" s="7" t="n">
@@ -7269,14 +7269,14 @@
         <v>108505</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1.3468</v>
+        <v>1.3782</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>1.67e+33</v>
+        <v>1.64e+33</v>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>1.67ag</t>
+          <t>1.64ag</t>
         </is>
       </c>
       <c r="I138" s="7" t="n">
@@ -7318,14 +7318,14 @@
         <v>111625</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1.4012</v>
+        <v>1.4024</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>2.34e+33</v>
+        <v>2.3e+33</v>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>2.34ag</t>
+          <t>2.3ag</t>
         </is>
       </c>
       <c r="I139" s="7" t="n">
@@ -7367,14 +7367,14 @@
         <v>114820</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1.3162</v>
+        <v>1.3348</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>3.08e+33</v>
+        <v>3.07e+33</v>
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>3.08ag</t>
+          <t>3.07ag</t>
         </is>
       </c>
       <c r="I140" s="7" t="n">
@@ -7416,14 +7416,14 @@
         <v>118095</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1.8247</v>
+        <v>1.4593</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>5.62e+33</v>
+        <v>4.48e+33</v>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>5.62ag</t>
+          <t>4.48ag</t>
         </is>
       </c>
       <c r="I141" s="7" t="n">
@@ -7465,14 +7465,14 @@
         <v>121450</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1.0249</v>
+        <v>1.154</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>5.76e+33</v>
+        <v>5.17e+33</v>
       </c>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>5.76ag</t>
+          <t>5.17ag</t>
         </is>
       </c>
       <c r="I142" s="7" t="n">
@@ -7514,14 +7514,14 @@
         <v>124890</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1.191</v>
+        <v>1.2998</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>6.86e+33</v>
+        <v>6.72e+33</v>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>6.86ag</t>
+          <t>6.72ag</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
@@ -7563,14 +7563,14 @@
         <v>128415</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1.3761</v>
+        <v>1.3735</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>9.439999999999999e+33</v>
+        <v>9.23e+33</v>
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>9.44ag</t>
+          <t>9.23ag</t>
         </is>
       </c>
       <c r="I144" s="7" t="n">
@@ -7612,14 +7612,14 @@
         <v>132030</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1.4831</v>
+        <v>1.4735</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1.4e+34</v>
+        <v>1.36e+34</v>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>14ag</t>
+          <t>13.6ag</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
@@ -7661,14 +7661,14 @@
         <v>135735</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1.1857</v>
+        <v>1.2059</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1.66e+34</v>
+        <v>1.64e+34</v>
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>16.6ag</t>
+          <t>16.4ag</t>
         </is>
       </c>
       <c r="I146" s="7" t="n">
@@ -7710,7 +7710,7 @@
         <v>139535</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1.3434</v>
+        <v>1.3598</v>
       </c>
       <c r="G147" s="5" t="n">
         <v>2.23e+34</v>
@@ -7759,14 +7759,14 @@
         <v>143430</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1.3857</v>
+        <v>1.3767</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>3.09e+34</v>
+        <v>3.07e+34</v>
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>30.9ag</t>
+          <t>30.7ag</t>
         </is>
       </c>
       <c r="I148" s="7" t="n">
@@ -7808,14 +7808,14 @@
         <v>147420</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1.4951</v>
+        <v>1.4104</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>4.62e+34</v>
+        <v>4.33e+34</v>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>46.1ag</t>
+          <t>43.3ag</t>
         </is>
       </c>
       <c r="I149" s="7" t="n">
@@ -7857,14 +7857,14 @@
         <v>151510</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1.2403</v>
+        <v>1.3256</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>5.73e+34</v>
+        <v>5.74e+34</v>
       </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>57.3ag</t>
+          <t>57.4ag</t>
         </is>
       </c>
       <c r="I150" s="7" t="n">
@@ -7906,14 +7906,14 @@
         <v>155705</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>1.3874</v>
+        <v>1.3868</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>7.95e+34</v>
+        <v>7.96e+34</v>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>79.5ag</t>
+          <t>79.6ag</t>
         </is>
       </c>
       <c r="I151" s="7" t="n">
